--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 13.10.2025 a 19.10.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 13.10.2025 a 19.10.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29415"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3AF1422-0E13-46F2-ACBE-24F20E271CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C52F1D81-F316-40D8-8425-EF62A618A19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="13.10" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="179">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -413,6 +413,225 @@
     <t>C
 onforme regra, apólice não completou 365 dias vigente , portanto d
 eve-se manter a classe de bônus, assim sendo o bônus correto 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ALBERTO DE OLIVEIRA BERTINO             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favor enviar cópia completa d
+a apólice anterior 2024/2025 ou CI atual </t>
+  </si>
+  <si>
+    <t>Nup CANCELAMENTO 15/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUVENAL ANTONIO DE OLIVEIRA JUNIOR           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NATALIA DOS SANTOS MELO                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO VINICIUS DA COSTA E SILVA              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALIRIO JUNIO BOMFIM LIMA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAURA MARIA RIBEIRO                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAELLA TAVARES DA SILVA                    </t>
+  </si>
+  <si>
+    <t>C
+onforme regra de apólices canceladas por vigência de curto prazo,
+houve quebra de vigência de 88 dias, portanto deve-se reduzir dua
+s classes de bônus, assim sendo o correto bônus 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOMINGOS FAVARON FILHO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HILANA CAVALCANTI DE OLIVEIRA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANILO SZILLAGY                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECUSA: SEGURADO NÃO CORRIGIU AS FOTOS - PRAZO INSPIRADO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS AURELIO SOARES FRAGOSO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSIVALDO RIBEIRO                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRUNO CARLOS DE OLIVEIRA SILVA               </t>
+  </si>
+  <si>
+    <t>VITOR IGOR POLONI GONCALVES | CPF: 09317456910</t>
+  </si>
+  <si>
+    <t>INDUSTRIA E COMERCIO DE CONFECCOES ARAUJO CHA</t>
+  </si>
+  <si>
+    <t>C
+onforme regra de apólices canceladas houve quebra de vigência de 4
+91 dias portanto devem-se excluir todas as classes de bônus e con
+siderar como seguro novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YASMIM PEREIRA DUARTE                        </t>
+  </si>
+  <si>
+    <t>C
+onforme regra de apólices canceladas por vigência de curto prazo,
+houve quebra de vigência de 53 dias, portanto deve-se reduzir UMA
+classe de bônus, assim sendo o correto bônus 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERVICOS E ENGENHARIA ELETRICA LTDA EPP      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LORRAN GUSTAVO SOUZA SILVA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABRIELA PANTOJA FAGUNDES                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Id
+entificamos que a proposta foi transmitida com bônus 10, conforme
+CBE bonificação está incorreta, apólice anterior consta classe de
+bônus3, não havendo sinistro, conforme regra concede 1 classe de b
+ônus, assim sendo o correto bônus 4. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRASIL DISTRIBUIDORA UTILIDADES E PESCA LTDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRITO SOLAR LTDA ME                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE MARCIO MENDES                           </t>
+  </si>
+  <si>
+    <t>Correção de Bônus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALICE SILVA SANTOS                           </t>
+  </si>
+  <si>
+    <t>RECUSA: SEGURADO NÃO CORRIGIU AS FOTOS - PRAZO INSPIRADO Fotos: Documento do veículo, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVANDRO LUIZ DE LIMA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NATALIA PERPETUA STEFANINI MARQUES           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIGIA MARIA SILVA DE MORAES CARVALHO         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO ROBERTO HONORIO DE MELO FILHO          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROBERTA GOMES RASMUSSEN                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MV COMERCIO DE PESCADOS LTDA ME              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAURO REIS DAMASCENO SOUZA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVERTON DE ASSIS FURTADO ALMEIDA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELO DE OLIVEIRA BRITO                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JANGADEIROS BURGUER LTDA ME                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BONUS SOLAR COMERCIO E IMPORTACAO LTDA EPP   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACILDA FERREIRA                             </t>
+  </si>
+  <si>
+    <t>MARCUS ANTONIO DE MELO SILVA CHURRASQUEIRO ME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARILENA MONTEIRO DE LIMA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAIKIELE BATISTA MARTINS PAES                </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que a
+apólice consta ativa na congênere, para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido, a atualização junto a Central de Bô
+nus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDIARA BARBOZA DE FREITAS FILHO             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREA ROMERO DE SOUZA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THALES AMORIM ARAGAO                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE WILSON CUNHA ALVES                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSANA MARIA FAUSTINO MONFRINATI             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral ESQUERD/DIREIT, Traseira e lateral ESQ, Porta </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IZABETH SILVINO DE CASTRO MARQUES DA SILVA   </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Painel com carro ligado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BENEDITO ROBERTO MASTRANDEA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Chassi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMARO FLOR DE ARAUJO                         </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do passageiro e do motorista, Traseira e lateral do motorista e do passageiro, Painel, Chassi, CRLV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALQUIRIA FERREIRA DE SOUSA                  </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTOS INCORRETAS: Frente e lateral do passageiro e do motorista, Painel com carro ligado, Chassi, Porta malas aberto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDIONIR VARIANI                           </t>
+  </si>
+  <si>
+    <t>A apólice enviada foi uma apólice de curto prazo que finalizou em
+03/12/2024 mais de 335 dias em relação a vigência desta proposta.
+Caso o cliente não tenha outra apólice será necessário recusar est
+aproposta e transmitir outra como seguro novo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILLKVEST JEANS LTDA ME                      </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: CRLV, Frente e lateral do motorista, Traseira e lateral do passageiro, Painel, Porta malas aberto.</t>
   </si>
 </sst>
 </file>
@@ -697,7 +916,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -779,34 +998,13 @@
     <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -869,7 +1067,41 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1269,10 +1501,10 @@
       <c r="G2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="52" t="s">
+      <c r="H2" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="51"/>
+      <c r="I2" s="42"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -1284,22 +1516,22 @@
       <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="50">
+      <c r="D3" s="41">
         <v>134776124</v>
       </c>
       <c r="E3" s="18">
         <v>3450099136</v>
       </c>
-      <c r="F3" s="46" t="s">
+      <c r="F3" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="52" t="s">
+      <c r="H3" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="51">
+      <c r="I3" s="42">
         <v>45933</v>
       </c>
     </row>
@@ -1313,22 +1545,22 @@
       <c r="C4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="50">
+      <c r="D4" s="41">
         <v>134783693</v>
       </c>
       <c r="E4" s="18">
         <v>3450099554</v>
       </c>
-      <c r="F4" s="46" t="s">
+      <c r="F4" s="37" t="s">
         <v>18</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="52" t="s">
+      <c r="H4" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="51">
+      <c r="I4" s="42">
         <v>45940</v>
       </c>
     </row>
@@ -1342,22 +1574,22 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="50">
+      <c r="D5" s="41">
         <v>134811284</v>
       </c>
       <c r="E5" s="18">
         <v>3450100445</v>
       </c>
-      <c r="F5" s="46" t="s">
+      <c r="F5" s="37" t="s">
         <v>21</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="52" t="s">
+      <c r="H5" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="42">
         <v>45940</v>
       </c>
     </row>
@@ -1371,22 +1603,22 @@
       <c r="C6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="50">
+      <c r="D6" s="41">
         <v>134843994</v>
       </c>
       <c r="E6" s="18">
         <v>3450101930</v>
       </c>
-      <c r="F6" s="46" t="s">
+      <c r="F6" s="37" t="s">
         <v>23</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="53" t="s">
+      <c r="H6" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="51">
+      <c r="I6" s="42">
         <v>45938</v>
       </c>
     </row>
@@ -1400,22 +1632,22 @@
       <c r="C7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="50">
+      <c r="D7" s="41">
         <v>134848027</v>
       </c>
       <c r="E7" s="18">
         <v>3450102249</v>
       </c>
-      <c r="F7" s="46" t="s">
+      <c r="F7" s="37" t="s">
         <v>26</v>
       </c>
       <c r="G7" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="54" t="s">
+      <c r="H7" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="51">
+      <c r="I7" s="42">
         <v>45938</v>
       </c>
     </row>
@@ -1429,22 +1661,22 @@
       <c r="C8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="50">
+      <c r="D8" s="41">
         <v>134862226</v>
       </c>
       <c r="E8" s="18">
         <v>3450103184</v>
       </c>
-      <c r="F8" s="46" t="s">
+      <c r="F8" s="37" t="s">
         <v>28</v>
       </c>
       <c r="G8" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="54" t="s">
+      <c r="H8" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="51">
+      <c r="I8" s="42">
         <v>45939</v>
       </c>
     </row>
@@ -1458,22 +1690,22 @@
       <c r="C9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="50">
+      <c r="D9" s="41">
         <v>134848561</v>
       </c>
       <c r="E9" s="18">
         <v>3450102293</v>
       </c>
-      <c r="F9" s="46" t="s">
+      <c r="F9" s="37" t="s">
         <v>29</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="55" t="s">
+      <c r="H9" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="51">
+      <c r="I9" s="42">
         <v>45938</v>
       </c>
     </row>
@@ -1487,22 +1719,22 @@
       <c r="C10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="50">
+      <c r="D10" s="41">
         <v>134902600</v>
       </c>
       <c r="E10" s="18">
         <v>3450105615</v>
       </c>
-      <c r="F10" s="46" t="s">
+      <c r="F10" s="37" t="s">
         <v>30</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="52" t="s">
+      <c r="H10" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="51">
+      <c r="I10" s="42">
         <v>45943</v>
       </c>
     </row>
@@ -1516,22 +1748,22 @@
       <c r="C11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="50">
+      <c r="D11" s="41">
         <v>134724498</v>
       </c>
       <c r="E11" s="18">
         <v>3450096375</v>
       </c>
-      <c r="F11" s="46" t="s">
+      <c r="F11" s="37" t="s">
         <v>31</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="52" t="s">
+      <c r="H11" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="I11" s="51">
+      <c r="I11" s="42">
         <v>45938</v>
       </c>
     </row>
@@ -1545,22 +1777,22 @@
       <c r="C12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="50">
+      <c r="D12" s="41">
         <v>134816739</v>
       </c>
       <c r="E12" s="18">
         <v>3450100797</v>
       </c>
-      <c r="F12" s="46" t="s">
+      <c r="F12" s="37" t="s">
         <v>34</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="52" t="s">
+      <c r="H12" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="I12" s="51">
+      <c r="I12" s="42">
         <v>45943</v>
       </c>
     </row>
@@ -1574,22 +1806,22 @@
       <c r="C13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="50">
+      <c r="D13" s="41">
         <v>134848220</v>
       </c>
       <c r="E13" s="18">
         <v>3450102260</v>
       </c>
-      <c r="F13" s="46" t="s">
+      <c r="F13" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H13" s="52" t="s">
+      <c r="H13" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="I13" s="51">
+      <c r="I13" s="42">
         <v>45938</v>
       </c>
     </row>
@@ -1603,22 +1835,22 @@
       <c r="C14" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="50">
+      <c r="D14" s="41">
         <v>134772495</v>
       </c>
       <c r="E14" s="18">
         <v>3450098938</v>
       </c>
-      <c r="F14" s="46" t="s">
+      <c r="F14" s="37" t="s">
         <v>37</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="52" t="s">
+      <c r="H14" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="51">
+      <c r="I14" s="42">
         <v>45933</v>
       </c>
     </row>
@@ -1632,22 +1864,22 @@
       <c r="C15" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="50">
+      <c r="D15" s="41">
         <v>134772604</v>
       </c>
       <c r="E15" s="18">
         <v>3450098949</v>
       </c>
-      <c r="F15" s="46" t="s">
+      <c r="F15" s="37" t="s">
         <v>38</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="52" t="s">
+      <c r="H15" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I15" s="51">
+      <c r="I15" s="42">
         <v>45933</v>
       </c>
     </row>
@@ -1661,22 +1893,22 @@
       <c r="C16" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="50">
+      <c r="D16" s="41">
         <v>134772998</v>
       </c>
       <c r="E16" s="18">
         <v>3450098982</v>
       </c>
-      <c r="F16" s="46" t="s">
+      <c r="F16" s="37" t="s">
         <v>39</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="52" t="s">
+      <c r="H16" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="51">
+      <c r="I16" s="42">
         <v>45933</v>
       </c>
     </row>
@@ -1684,9 +1916,9 @@
       <c r="A17" s="6"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="49"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="40"/>
       <c r="G17" s="20"/>
       <c r="H17" s="9"/>
       <c r="I17" s="27"/>
@@ -2150,7 +2382,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="59" t="s">
+      <c r="H1" s="50" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -2167,10 +2399,10 @@
       <c r="C2" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="57">
+      <c r="E2" s="48">
         <v>3450104900</v>
       </c>
       <c r="F2" s="31" t="s">
@@ -2179,10 +2411,10 @@
       <c r="G2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="58" t="s">
+      <c r="H2" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="51"/>
+      <c r="I2" s="42"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -2206,10 +2438,10 @@
       <c r="G3" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="60" t="s">
+      <c r="H3" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="51">
+      <c r="I3" s="42">
         <v>45936</v>
       </c>
     </row>
@@ -2235,10 +2467,10 @@
       <c r="G4" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="52" t="s">
+      <c r="H4" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="51">
+      <c r="I4" s="42">
         <v>45936</v>
       </c>
     </row>
@@ -2264,10 +2496,10 @@
       <c r="G5" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="52" t="s">
+      <c r="H5" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="42">
         <v>45936</v>
       </c>
     </row>
@@ -2293,10 +2525,10 @@
       <c r="G6" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="52" t="s">
+      <c r="H6" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="51">
+      <c r="I6" s="42">
         <v>45931</v>
       </c>
     </row>
@@ -2322,10 +2554,10 @@
       <c r="G7" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="52" t="s">
+      <c r="H7" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="51">
+      <c r="I7" s="42">
         <v>45943</v>
       </c>
     </row>
@@ -2351,10 +2583,10 @@
       <c r="G8" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="52" t="s">
+      <c r="H8" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="I8" s="51">
+      <c r="I8" s="42">
         <v>45943</v>
       </c>
     </row>
@@ -2380,10 +2612,10 @@
       <c r="G9" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="52" t="s">
+      <c r="H9" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="I9" s="51">
+      <c r="I9" s="42">
         <v>45939</v>
       </c>
     </row>
@@ -2409,10 +2641,10 @@
       <c r="G10" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="52" t="s">
+      <c r="H10" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="51">
+      <c r="I10" s="42">
         <v>45940</v>
       </c>
     </row>
@@ -2438,10 +2670,10 @@
       <c r="G11" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="52" t="s">
+      <c r="H11" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="51">
+      <c r="I11" s="42">
         <v>45943</v>
       </c>
     </row>
@@ -2467,10 +2699,10 @@
       <c r="G12" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="52" t="s">
+      <c r="H12" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="I12" s="51">
+      <c r="I12" s="42">
         <v>45943</v>
       </c>
     </row>
@@ -2496,10 +2728,10 @@
       <c r="G13" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="52" t="s">
+      <c r="H13" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I13" s="51">
+      <c r="I13" s="42">
         <v>45931</v>
       </c>
     </row>
@@ -2525,10 +2757,10 @@
       <c r="G14" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="52" t="s">
+      <c r="H14" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="I14" s="51">
+      <c r="I14" s="42">
         <v>45943</v>
       </c>
     </row>
@@ -2554,10 +2786,10 @@
       <c r="G15" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="52" t="s">
+      <c r="H15" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="I15" s="51">
+      <c r="I15" s="42">
         <v>45932</v>
       </c>
     </row>
@@ -2583,10 +2815,10 @@
       <c r="G16" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="52" t="s">
+      <c r="H16" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="I16" s="51">
+      <c r="I16" s="42">
         <v>45938</v>
       </c>
     </row>
@@ -2612,10 +2844,10 @@
       <c r="G17" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="52" t="s">
+      <c r="H17" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="I17" s="51">
+      <c r="I17" s="42">
         <v>45944</v>
       </c>
     </row>
@@ -2641,10 +2873,10 @@
       <c r="G18" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="52" t="s">
+      <c r="H18" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="I18" s="51">
+      <c r="I18" s="42">
         <v>45943</v>
       </c>
     </row>
@@ -2670,10 +2902,10 @@
       <c r="G19" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="H19" s="52" t="s">
+      <c r="H19" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="51">
+      <c r="I19" s="42">
         <v>45939</v>
       </c>
     </row>
@@ -2699,10 +2931,10 @@
       <c r="G20" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="52" t="s">
+      <c r="H20" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="I20" s="51">
+      <c r="I20" s="42">
         <v>45937</v>
       </c>
     </row>
@@ -2728,10 +2960,10 @@
       <c r="G21" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="H21" s="52" t="s">
+      <c r="H21" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="I21" s="51">
+      <c r="I21" s="42">
         <v>45938</v>
       </c>
     </row>
@@ -2757,10 +2989,10 @@
       <c r="G22" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H22" s="52" t="s">
+      <c r="H22" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I22" s="51">
+      <c r="I22" s="42">
         <v>45933</v>
       </c>
     </row>
@@ -2786,10 +3018,10 @@
       <c r="G23" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H23" s="52" t="s">
+      <c r="H23" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I23" s="51">
+      <c r="I23" s="42">
         <v>45936</v>
       </c>
     </row>
@@ -2815,10 +3047,10 @@
       <c r="G24" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H24" s="52" t="s">
+      <c r="H24" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I24" s="51">
+      <c r="I24" s="42">
         <v>45933</v>
       </c>
     </row>
@@ -2844,10 +3076,10 @@
       <c r="G25" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H25" s="52" t="s">
+      <c r="H25" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I25" s="51">
+      <c r="I25" s="42">
         <v>45933</v>
       </c>
     </row>
@@ -2873,10 +3105,10 @@
       <c r="G26" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H26" s="52" t="s">
+      <c r="H26" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I26" s="51">
+      <c r="I26" s="42">
         <v>45933</v>
       </c>
     </row>
@@ -2902,10 +3134,10 @@
       <c r="G27" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H27" s="52" t="s">
+      <c r="H27" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I27" s="51">
+      <c r="I27" s="42">
         <v>45933</v>
       </c>
     </row>
@@ -2931,10 +3163,10 @@
       <c r="G28" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H28" s="52" t="s">
+      <c r="H28" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I28" s="51">
+      <c r="I28" s="42">
         <v>45936</v>
       </c>
     </row>
@@ -2960,10 +3192,10 @@
       <c r="G29" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H29" s="52" t="s">
+      <c r="H29" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I29" s="51">
+      <c r="I29" s="42">
         <v>45936</v>
       </c>
     </row>
@@ -3264,7 +3496,7 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="70">
+      <c r="B2" s="61">
         <v>45937</v>
       </c>
       <c r="C2" s="28">
@@ -3282,43 +3514,43 @@
       <c r="G2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="68" t="s">
+      <c r="H2" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="I2" s="67"/>
+      <c r="I2" s="58"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="70">
+      <c r="B3" s="61">
         <v>45943</v>
       </c>
       <c r="C3" s="28">
         <v>45945</v>
       </c>
-      <c r="D3" s="63" t="s">
+      <c r="D3" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="57">
+      <c r="E3" s="48">
         <v>3450106715</v>
       </c>
       <c r="F3" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="G3" s="64" t="s">
+      <c r="G3" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="68" t="s">
+      <c r="H3" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="I3" s="51"/>
+      <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="70">
+      <c r="B4" s="61">
         <v>45940</v>
       </c>
       <c r="C4" s="28">
@@ -3333,13 +3565,13 @@
       <c r="F4" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="G4" s="61" t="s">
+      <c r="G4" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="68" t="s">
+      <c r="H4" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="I4" s="51">
+      <c r="I4" s="42">
         <v>45944</v>
       </c>
     </row>
@@ -3347,7 +3579,7 @@
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="70">
+      <c r="B5" s="61">
         <v>45940</v>
       </c>
       <c r="C5" s="28">
@@ -3362,13 +3594,13 @@
       <c r="F5" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="G5" s="61" t="s">
+      <c r="G5" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="69" t="s">
+      <c r="H5" s="60" t="s">
         <v>87</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="42">
         <v>45940</v>
       </c>
     </row>
@@ -3376,7 +3608,7 @@
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="70">
+      <c r="B6" s="61">
         <v>45943</v>
       </c>
       <c r="C6" s="28">
@@ -3391,13 +3623,13 @@
       <c r="F6" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="G6" s="61" t="s">
+      <c r="G6" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="69" t="s">
+      <c r="H6" s="60" t="s">
         <v>85</v>
       </c>
-      <c r="I6" s="51">
+      <c r="I6" s="42">
         <v>45944</v>
       </c>
     </row>
@@ -3405,7 +3637,7 @@
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="70">
+      <c r="B7" s="61">
         <v>45943</v>
       </c>
       <c r="C7" s="28">
@@ -3420,13 +3652,13 @@
       <c r="F7" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="G7" s="61" t="s">
+      <c r="G7" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="71" t="s">
+      <c r="H7" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="I7" s="51">
+      <c r="I7" s="42">
         <v>45945</v>
       </c>
     </row>
@@ -3434,7 +3666,7 @@
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="70">
+      <c r="B8" s="61">
         <v>45943</v>
       </c>
       <c r="C8" s="28">
@@ -3449,13 +3681,13 @@
       <c r="F8" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G8" s="61" t="s">
+      <c r="G8" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="71" t="s">
+      <c r="H8" s="60" t="s">
         <v>85</v>
       </c>
-      <c r="I8" s="51">
+      <c r="I8" s="42">
         <v>45944</v>
       </c>
     </row>
@@ -3463,7 +3695,7 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="70">
+      <c r="B9" s="61">
         <v>45943</v>
       </c>
       <c r="C9" s="28">
@@ -3478,13 +3710,13 @@
       <c r="F9" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="G9" s="62" t="s">
+      <c r="G9" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="69" t="s">
+      <c r="H9" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="51">
+      <c r="I9" s="42">
         <v>45943</v>
       </c>
     </row>
@@ -3492,7 +3724,7 @@
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="70">
+      <c r="B10" s="61">
         <v>45944</v>
       </c>
       <c r="C10" s="28">
@@ -3507,13 +3739,13 @@
       <c r="F10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="61" t="s">
+      <c r="G10" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="69" t="s">
+      <c r="H10" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="51">
+      <c r="I10" s="42">
         <v>45944</v>
       </c>
     </row>
@@ -3521,7 +3753,7 @@
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="70">
+      <c r="B11" s="61">
         <v>45944</v>
       </c>
       <c r="C11" s="28">
@@ -3536,13 +3768,13 @@
       <c r="F11" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="G11" s="62" t="s">
+      <c r="G11" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="71" t="s">
+      <c r="H11" s="60" t="s">
         <v>94</v>
       </c>
-      <c r="I11" s="51">
+      <c r="I11" s="42">
         <v>45944</v>
       </c>
     </row>
@@ -3550,7 +3782,7 @@
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="70">
+      <c r="B12" s="61">
         <v>45944</v>
       </c>
       <c r="C12" s="28">
@@ -3565,13 +3797,13 @@
       <c r="F12" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="G12" s="61" t="s">
+      <c r="G12" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="69" t="s">
+      <c r="H12" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="I12" s="51">
+      <c r="I12" s="42">
         <v>45944</v>
       </c>
     </row>
@@ -3579,7 +3811,7 @@
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="70">
+      <c r="B13" s="61">
         <v>45937</v>
       </c>
       <c r="C13" s="28">
@@ -3594,13 +3826,13 @@
       <c r="F13" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="G13" s="61" t="s">
+      <c r="G13" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="H13" s="69" t="s">
+      <c r="H13" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="I13" s="51">
+      <c r="I13" s="42">
         <v>45937</v>
       </c>
     </row>
@@ -3608,7 +3840,7 @@
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="70">
+      <c r="B14" s="61">
         <v>45933</v>
       </c>
       <c r="C14" s="28">
@@ -3623,13 +3855,13 @@
       <c r="F14" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="G14" s="61" t="s">
+      <c r="G14" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="69" t="s">
+      <c r="H14" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="I14" s="51">
+      <c r="I14" s="42">
         <v>45945</v>
       </c>
     </row>
@@ -3637,7 +3869,7 @@
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="70">
+      <c r="B15" s="61">
         <v>45932</v>
       </c>
       <c r="C15" s="28">
@@ -3652,13 +3884,13 @@
       <c r="F15" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="61" t="s">
+      <c r="G15" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="71" t="s">
+      <c r="H15" s="60" t="s">
         <v>101</v>
       </c>
-      <c r="I15" s="51">
+      <c r="I15" s="42">
         <v>45939</v>
       </c>
     </row>
@@ -3666,7 +3898,7 @@
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="70">
+      <c r="B16" s="61">
         <v>45962</v>
       </c>
       <c r="C16" s="28">
@@ -3681,13 +3913,13 @@
       <c r="F16" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="71" t="s">
+      <c r="H16" s="60" t="s">
         <v>102</v>
       </c>
-      <c r="I16" s="51">
+      <c r="I16" s="42">
         <v>45939</v>
       </c>
     </row>
@@ -3710,13 +3942,13 @@
       <c r="F17" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="G17" s="61" t="s">
+      <c r="G17" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H17" s="69" t="s">
+      <c r="H17" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="I17" s="51">
+      <c r="I17" s="42">
         <v>45944</v>
       </c>
     </row>
@@ -3739,13 +3971,13 @@
       <c r="F18" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G18" s="61" t="s">
+      <c r="G18" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="H18" s="69" t="s">
+      <c r="H18" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="I18" s="51">
+      <c r="I18" s="42">
         <v>45940</v>
       </c>
     </row>
@@ -3768,13 +4000,13 @@
       <c r="F19" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="G19" s="61" t="s">
+      <c r="G19" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="H19" s="69" t="s">
+      <c r="H19" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="I19" s="51">
+      <c r="I19" s="42">
         <v>45937</v>
       </c>
     </row>
@@ -3797,13 +4029,13 @@
       <c r="F20" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="G20" s="61" t="s">
+      <c r="G20" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="H20" s="69" t="s">
+      <c r="H20" s="60" t="s">
         <v>109</v>
       </c>
-      <c r="I20" s="51">
+      <c r="I20" s="42">
         <v>45933</v>
       </c>
     </row>
@@ -3826,13 +4058,13 @@
       <c r="F21" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="G21" s="61" t="s">
+      <c r="G21" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="H21" s="69" t="s">
+      <c r="H21" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="I21" s="51">
+      <c r="I21" s="42">
         <v>45939</v>
       </c>
     </row>
@@ -3855,13 +4087,13 @@
       <c r="F22" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="G22" s="62" t="s">
+      <c r="G22" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="71" t="s">
+      <c r="H22" s="60" t="s">
         <v>112</v>
       </c>
-      <c r="I22" s="51">
+      <c r="I22" s="42">
         <v>45939</v>
       </c>
     </row>
@@ -3869,10 +4101,10 @@
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="28"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="66"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="57"/>
       <c r="H23" s="9"/>
     </row>
     <row r="24" spans="1:9">
@@ -4079,7 +4311,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF216D7-F2B3-4C54-A7B9-7048B06C2C75}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -4126,192 +4358,416 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="27"/>
+      <c r="B2" s="7">
+        <v>45939</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45946</v>
+      </c>
+      <c r="D2" s="25">
+        <v>134856844</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450102645</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="I2" s="42">
+        <v>45944</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="27"/>
+      <c r="B3" s="7">
+        <v>45944</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45946</v>
+      </c>
+      <c r="D3" s="25">
+        <v>134921585</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450107078</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="I3" s="42">
+        <v>45945</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="27"/>
+      <c r="B4" s="7">
+        <v>45944</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45946</v>
+      </c>
+      <c r="D4" s="25">
+        <v>134919110</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450106935</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="42">
+        <v>45944</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="27"/>
+      <c r="B5" s="7">
+        <v>45944</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45946</v>
+      </c>
+      <c r="D5" s="25">
+        <v>134921171</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450107056</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="42">
+        <v>45944</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="27"/>
+      <c r="B6" s="7">
+        <v>45945</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45946</v>
+      </c>
+      <c r="D6" s="25">
+        <v>134944976</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450108300</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="42">
+        <v>45945</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="27"/>
+      <c r="B7" s="7">
+        <v>45936</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45946</v>
+      </c>
+      <c r="D7" s="25">
+        <v>134873071</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450100159</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="42">
+        <v>45936</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="27"/>
+      <c r="B8" s="7">
+        <v>45945</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45946</v>
+      </c>
+      <c r="D8" s="25">
+        <v>134953488</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450108827</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="42">
+        <v>45947</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="27"/>
+      <c r="B9" s="7">
+        <v>45961</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45946</v>
+      </c>
+      <c r="D9" s="25">
+        <v>134831845</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450101314</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="I9" s="42">
+        <v>45944</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="27"/>
+      <c r="B10" s="7">
+        <v>45932</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45946</v>
+      </c>
+      <c r="D10" s="25">
+        <v>134747798</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450097750</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" s="42">
+        <v>45945</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="27"/>
+      <c r="B11" s="7">
+        <v>45933</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45946</v>
+      </c>
+      <c r="D11" s="25">
+        <v>134762243</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450098487</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="42">
+        <v>45939</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="27"/>
+      <c r="B12" s="7">
+        <v>45938</v>
+      </c>
+      <c r="C12" s="28">
+        <v>45946</v>
+      </c>
+      <c r="D12" s="25">
+        <v>134840802</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450101798</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="I12" s="42">
+        <v>45946</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="27"/>
+      <c r="B13" s="7">
+        <v>45951</v>
+      </c>
+      <c r="C13" s="28">
+        <v>45946</v>
+      </c>
+      <c r="D13" s="25">
+        <v>134845539</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450102084</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" s="42">
+        <v>45945</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="27"/>
+      <c r="B14" s="7">
+        <v>45960</v>
+      </c>
+      <c r="C14" s="28">
+        <v>45946</v>
+      </c>
+      <c r="D14" s="25">
+        <v>134835808</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450101446</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="I14" s="42">
+        <v>45945</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="27"/>
+      <c r="B15" s="7">
+        <v>45944</v>
+      </c>
+      <c r="C15" s="28">
+        <v>45946</v>
+      </c>
+      <c r="D15" s="25">
+        <v>134927735</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450107430</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="42">
+        <v>45944</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="30"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="6"/>
       <c r="H16" s="9"/>
       <c r="I16" s="27"/>
     </row>
@@ -4328,11 +4784,11 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
+      <c r="B18" s="8"/>
       <c r="C18" s="7"/>
       <c r="D18" s="8"/>
       <c r="E18" s="14"/>
-      <c r="F18" s="12"/>
+      <c r="F18" s="13"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
       <c r="I18" s="27"/>
@@ -4342,8 +4798,8 @@
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="13"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="15"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
       <c r="I19" s="27"/>
@@ -4354,10 +4810,9 @@
       <c r="C20" s="7"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
-      <c r="F20" s="15"/>
+      <c r="F20" s="9"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="27"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -4699,27 +5154,17 @@
       <c r="G54" s="6"/>
       <c r="H54" s="9"/>
     </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A17" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G40" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4729,7 +5174,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D38813-FAE5-45C6-9D51-7607EDAA916D}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -4765,7 +5210,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="36" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -4773,378 +5218,880 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="27"/>
+      <c r="A2" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="7">
+        <v>45950</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D2" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="48">
+        <v>3450101941</v>
+      </c>
+      <c r="F2" s="76" t="s">
+        <v>130</v>
+      </c>
+      <c r="G2" s="70" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="77"/>
+      <c r="I2" s="42"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="27"/>
+      <c r="B3" s="7">
+        <v>45937</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D3" s="63">
+        <v>134826721</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450101237</v>
+      </c>
+      <c r="F3" s="62" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="I3" s="78">
+        <v>45943</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="27"/>
+      <c r="B4" s="7">
+        <v>45938</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D4" s="63">
+        <v>134838938</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450101655</v>
+      </c>
+      <c r="F4" s="62" t="s">
+        <v>133</v>
+      </c>
+      <c r="G4" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="72" t="s">
+        <v>134</v>
+      </c>
+      <c r="I4" s="42">
+        <v>45944</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="27"/>
+      <c r="B5" s="7">
+        <v>45938</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D5" s="63">
+        <v>134838645</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450101600</v>
+      </c>
+      <c r="F5" s="62" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="42">
+        <v>45938</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="27"/>
+      <c r="B6" s="7">
+        <v>45939</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D6" s="63">
+        <v>134869500</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450103448</v>
+      </c>
+      <c r="F6" s="62" t="s">
+        <v>136</v>
+      </c>
+      <c r="G6" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="42">
+        <v>45939</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="27"/>
+      <c r="B7" s="7">
+        <v>45956</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D7" s="63">
+        <v>134910944</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450106363</v>
+      </c>
+      <c r="F7" s="62" t="s">
+        <v>137</v>
+      </c>
+      <c r="G7" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="73" t="s">
+        <v>138</v>
+      </c>
+      <c r="I7" s="42">
+        <v>45945</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="27"/>
+      <c r="B8" s="7">
+        <v>45944</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D8" s="63">
+        <v>134929230</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450107507</v>
+      </c>
+      <c r="F8" s="62" t="s">
+        <v>139</v>
+      </c>
+      <c r="G8" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="42">
+        <v>45944</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="27"/>
+      <c r="B9" s="7">
+        <v>45944</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D9" s="63">
+        <v>134933777</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450107826</v>
+      </c>
+      <c r="F9" s="62" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="42">
+        <v>45944</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="27"/>
+      <c r="B10" s="7">
+        <v>45946</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D10" s="63">
+        <v>134966232</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450109641</v>
+      </c>
+      <c r="F10" s="62" t="s">
+        <v>141</v>
+      </c>
+      <c r="G10" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="67" t="s">
+        <v>142</v>
+      </c>
+      <c r="I10" s="42">
+        <v>45947</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="27"/>
+      <c r="B11" s="7">
+        <v>45946</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D11" s="63">
+        <v>134964144</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450109410</v>
+      </c>
+      <c r="F11" s="62" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="42">
+        <v>45946</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="27"/>
+      <c r="B12" s="7">
+        <v>45939</v>
+      </c>
+      <c r="C12" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D12" s="63">
+        <v>134860076</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450102975</v>
+      </c>
+      <c r="F12" s="62" t="s">
+        <v>143</v>
+      </c>
+      <c r="G12" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="72" t="s">
+        <v>144</v>
+      </c>
+      <c r="I12" s="42">
+        <v>45939</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="27"/>
+      <c r="B13" s="7">
+        <v>45939</v>
+      </c>
+      <c r="C13" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D13" s="63">
+        <v>134869548</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450103503</v>
+      </c>
+      <c r="F13" s="62" t="s">
+        <v>145</v>
+      </c>
+      <c r="G13" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="67" t="s">
+        <v>109</v>
+      </c>
+      <c r="I13" s="42">
+        <v>45939</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="27"/>
+      <c r="B14" s="7">
+        <v>45971</v>
+      </c>
+      <c r="C14" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D14" s="63">
+        <v>134988983</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450105802</v>
+      </c>
+      <c r="F14" s="62" t="s">
+        <v>146</v>
+      </c>
+      <c r="G14" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="42">
+        <v>45971</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="27"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="27"/>
-    </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="27"/>
+      <c r="B15" s="7">
+        <v>45938</v>
+      </c>
+      <c r="C15" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D15" s="63">
+        <v>134839437</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450101732</v>
+      </c>
+      <c r="F15" s="62" t="s">
+        <v>147</v>
+      </c>
+      <c r="G15" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="42">
+        <v>45938</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15" customHeight="1">
+      <c r="A16" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>45938</v>
+      </c>
+      <c r="C16" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D16" s="63">
+        <v>134842546</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450101831</v>
+      </c>
+      <c r="F16" s="62" t="s">
+        <v>148</v>
+      </c>
+      <c r="G16" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="42">
+        <v>45938</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45938</v>
+      </c>
+      <c r="C17" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D17" s="63">
+        <v>134844371</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450101996</v>
+      </c>
+      <c r="F17" s="62" t="s">
+        <v>149</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="42">
+        <v>45938</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="27"/>
+      <c r="B18" s="7">
+        <v>45938</v>
+      </c>
+      <c r="C18" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D18" s="63">
+        <v>134847539</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450102205</v>
+      </c>
+      <c r="F18" s="62" t="s">
+        <v>150</v>
+      </c>
+      <c r="G18" s="69" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="42">
+        <v>45938</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="27"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45938</v>
+      </c>
+      <c r="C19" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D19" s="63">
+        <v>134847996</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450102238</v>
+      </c>
+      <c r="F19" s="62" t="s">
+        <v>151</v>
+      </c>
+      <c r="G19" s="69" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="42">
+        <v>45938</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="27"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45938</v>
+      </c>
+      <c r="C20" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D20" s="63">
+        <v>134849889</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450102425</v>
+      </c>
+      <c r="F20" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="G20" s="69" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="42">
+        <v>45938</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="27"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45936</v>
+      </c>
+      <c r="C21" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D21" s="63">
+        <v>134852830</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450100335</v>
+      </c>
+      <c r="F21" s="62" t="s">
+        <v>153</v>
+      </c>
+      <c r="G21" s="69" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="42">
+        <v>45936</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="27"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45939</v>
+      </c>
+      <c r="C22" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D22" s="63">
+        <v>134854093</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450102513</v>
+      </c>
+      <c r="F22" s="62" t="s">
+        <v>154</v>
+      </c>
+      <c r="G22" s="69" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="42">
+        <v>45939</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="27"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45939</v>
+      </c>
+      <c r="C23" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D23" s="63">
+        <v>134854982</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450102557</v>
+      </c>
+      <c r="F23" s="62" t="s">
+        <v>155</v>
+      </c>
+      <c r="G23" s="69" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="42">
+        <v>45939</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="27"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45939</v>
+      </c>
+      <c r="C24" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D24" s="63">
+        <v>134857172</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3450102689</v>
+      </c>
+      <c r="F24" s="62" t="s">
+        <v>156</v>
+      </c>
+      <c r="G24" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="42">
+        <v>45939</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="27"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45939</v>
+      </c>
+      <c r="C25" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D25" s="63">
+        <v>134860535</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3450103019</v>
+      </c>
+      <c r="F25" s="62" t="s">
+        <v>157</v>
+      </c>
+      <c r="G25" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="42">
+        <v>45939</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="27"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45937</v>
+      </c>
+      <c r="C26" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D26" s="63">
+        <v>134813625</v>
+      </c>
+      <c r="E26" s="18">
+        <v>3450100490</v>
+      </c>
+      <c r="F26" s="62" t="s">
+        <v>158</v>
+      </c>
+      <c r="G26" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="42">
+        <v>45937</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="27"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45937</v>
+      </c>
+      <c r="C27" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D27" s="63">
+        <v>134814178</v>
+      </c>
+      <c r="E27" s="18">
+        <v>3450100522</v>
+      </c>
+      <c r="F27" s="62" t="s">
+        <v>159</v>
+      </c>
+      <c r="G27" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="H27" s="74" t="s">
+        <v>160</v>
+      </c>
+      <c r="I27" s="42">
+        <v>45943</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="27"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45937</v>
+      </c>
+      <c r="C28" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D28" s="63">
+        <v>134814240</v>
+      </c>
+      <c r="E28" s="18">
+        <v>3450100533</v>
+      </c>
+      <c r="F28" s="62" t="s">
+        <v>161</v>
+      </c>
+      <c r="G28" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="42">
+        <v>45937</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="27"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45937</v>
+      </c>
+      <c r="C29" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D29" s="63">
+        <v>134814818</v>
+      </c>
+      <c r="E29" s="18">
+        <v>3450100566</v>
+      </c>
+      <c r="F29" s="62" t="s">
+        <v>162</v>
+      </c>
+      <c r="G29" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="42">
+        <v>45937</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="27"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>45933</v>
+      </c>
+      <c r="C30" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D30" s="63">
+        <v>134818587</v>
+      </c>
+      <c r="E30" s="18">
+        <v>3450098773</v>
+      </c>
+      <c r="F30" s="62" t="s">
+        <v>163</v>
+      </c>
+      <c r="G30" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" s="42">
+        <v>45933</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="27"/>
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>45933</v>
+      </c>
+      <c r="C31" s="28">
+        <v>45947</v>
+      </c>
+      <c r="D31" s="63">
+        <v>134818815</v>
+      </c>
+      <c r="E31" s="18">
+        <v>3450098696</v>
+      </c>
+      <c r="F31" s="62" t="s">
+        <v>164</v>
+      </c>
+      <c r="G31" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" s="42">
+        <v>45933</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="8"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="15"/>
       <c r="I32" s="27"/>
     </row>
     <row r="33" spans="1:9">
@@ -5178,7 +6125,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="27"/>
+      <c r="I35"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -5389,28 +6336,17 @@
       <c r="H54" s="9"/>
       <c r="I54"/>
     </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-      <c r="I55"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A31" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G40" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5420,7 +6356,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B760CA2F-2CA8-44F2-8B49-339714F538DA}">
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
@@ -5429,7 +6365,7 @@
     <col min="5" max="5" width="16.85546875" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
     <col min="7" max="7" width="19.42578125" customWidth="1"/>
-    <col min="8" max="8" width="24.7109375" customWidth="1"/>
+    <col min="8" max="8" width="27.85546875" customWidth="1"/>
     <col min="9" max="9" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5466,94 +6402,212 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="27"/>
+      <c r="B2" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45948</v>
+      </c>
+      <c r="D2" s="63">
+        <v>134878294</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450103877</v>
+      </c>
+      <c r="F2" s="62" t="s">
+        <v>165</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="I2" s="64">
+        <v>45940</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="37"/>
+      <c r="B3" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45948</v>
+      </c>
+      <c r="D3" s="63">
+        <v>134893359</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450105076</v>
+      </c>
+      <c r="F3" s="62" t="s">
+        <v>167</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="I3" s="42">
+        <v>45940</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="27"/>
+      <c r="B4" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45948</v>
+      </c>
+      <c r="D4" s="63">
+        <v>134881062</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450104229</v>
+      </c>
+      <c r="F4" s="62" t="s">
+        <v>169</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="I4" s="42">
+        <v>45940</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="27"/>
+      <c r="B5" s="7">
+        <v>45937</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45948</v>
+      </c>
+      <c r="D5" s="63">
+        <v>134874668</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450100610</v>
+      </c>
+      <c r="F5" s="62" t="s">
+        <v>171</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="43" t="s">
+        <v>172</v>
+      </c>
+      <c r="I5" s="42">
+        <v>45937</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="27"/>
+      <c r="A6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45948</v>
+      </c>
+      <c r="D6" s="63">
+        <v>134891446</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450104955</v>
+      </c>
+      <c r="F6" s="62" t="s">
+        <v>173</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="I6" s="42">
+        <v>45940</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="11"/>
+      <c r="A7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="7">
+        <v>45964</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45948</v>
+      </c>
+      <c r="D7" s="63">
+        <v>134826952</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450101182</v>
+      </c>
+      <c r="F7" s="62" t="s">
+        <v>175</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="65" t="s">
+        <v>176</v>
+      </c>
+      <c r="I7" s="42">
+        <v>45939</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="11"/>
+      <c r="A8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="7">
+        <v>45940</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45948</v>
+      </c>
+      <c r="D8" s="63">
+        <v>134876679</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450103723</v>
+      </c>
+      <c r="F8" s="62" t="s">
+        <v>177</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="I8" s="42">
+        <v>45940</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="34"/>
       <c r="G9" s="6"/>
       <c r="H9" s="9"/>
       <c r="I9" s="11"/>
@@ -5615,22 +6669,21 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="7"/>
       <c r="D15" s="8"/>
       <c r="E15" s="14"/>
-      <c r="F15" s="12"/>
+      <c r="F15" s="13"/>
       <c r="G15" s="6"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="8"/>
       <c r="C16" s="7"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="13"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="15"/>
       <c r="G16" s="6"/>
       <c r="H16" s="9"/>
     </row>
@@ -5640,7 +6693,7 @@
       <c r="C17" s="7"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="15"/>
+      <c r="F17" s="9"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
     </row>
@@ -5984,28 +7037,18 @@
       <c r="G51" s="6"/>
       <c r="H51" s="9"/>
     </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G38" xr:uid="{F491B589-3891-4413-A332-CE5A1AB48EB2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G37" xr:uid="{F491B589-3891-4413-A332-CE5A1AB48EB2}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A15" xr:uid="{D22D2853-2B53-4F60-8CBE-3EBA3A5BA43C}">
-      <formula1>$J$2</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A14" xr:uid="{D22D2853-2B53-4F60-8CBE-3EBA3A5BA43C}">
+      <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6674,51 +7717,58 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496595</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496595</Url>
-      <Description>QAFFA7D2F2TC-2102087286-496595</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac14f8cb44178d381f4c0afb30680a90">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58414b065c9b590c40efa77cd84bb6" ns1:_="" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="0b21122b788e66690c7828fa6fbd4a35">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8036ee6e27b0b3bdae29363f3ddd68e9" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -6767,12 +7817,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -6781,12 +7831,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -6869,7 +7919,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -6888,7 +7938,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -6921,7 +7971,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -7004,8 +8054,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -7095,53 +8145,46 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496595</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496595</Url>
+      <Description>QAFFA7D2F2TC-2102087286-496595</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7149,13 +8192,13 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F509BA6F-2750-4F9D-B040-E44B89BEA6B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B48707-C0CB-44F3-BDCA-8AC11FA02F8A}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>